--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20261004.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20261004.xlsx
@@ -12203,7 +12203,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>**第6版（5章＋資料編・84表・図3点）。****第4章④に「人材の供給制約からみた見込量の妥当性」と「見える化システムによる算定との突合」を加えた。****第4章 基本目標2に「⑦ 在宅医療・介護連携の推進」を新設し、国の評価指標が求める4つの場面（日常の療養支援・入退院支援・急変時の対応・看取り）ごとの目指すべき姿を掲げた。****基本目標3① の介護給付適正化の記述を、令和8年度交付金の実際の得点に合わせて訂正した**（主要3事業は3つとも実施、医療情報との突合は全国上位1割。0点はケアプラン点検の実施割合だけ）。**項目別の得点そのものは計画本文には置かず、評価から読み取れる中身と協議会への報告手順のみを書いている。**12施策すべてに現状と課題・施策の方向・主な事業・成果指標を記載。**第2版の未確定158箇所のうち61箇所が解消し97箇所となった。**第2章6（被保険者数・認定者数の見込み）を第10期将来推計用推計人口で確定し、第4章③にサービス見込量・給付費・標準給付費・地域支援事業費の事業別内訳・保険料基準額を入れた。**第5版（9月25日）で令和8年度の置き方を自然体推計に改め、保険料基準額は月額6,402円から6,048円（切上げ6,100円）となった。****9月25日の再検証で、延ばし方を見える化システムの仕様にそろえた**（施設は利用者数一定、居住系・在宅は認定者数で延ばす。月額▲13円）。従前の方式による算定は比較のケースとして残している。**第5章2の進行管理に、保険者機能強化推進交付金等の評価結果を点検項目として加えた**（評価結果を外部の議論の場で検証すること自体が評価指標の要件であるため）</t>
+          <t>**第8版（6章＋資料編・104表・図5点・見出し45件）。****10月4日に、他団体の計画との対比で残っていた3項目を埋めた**（第6章10 中長期の見通し／第1章2 の制度改正の表／資料編12 図表番号一覧）。**すべての表に通し番号を振り、表題は見出しから機械的に作る形にした。**未確定は136箇所（町データ待ち62／協議会で設定55／決定後に記載13／見える化出力待ち6）で、**受託者が算定すべきものは引き続き0件である**（新しい節を立てたぶん町データ待ちと協議会で設定が増えている）。**第6版（5章＋資料編・84表・図3点）。****第4章④に「人材の供給制約からみた見込量の妥当性」と「見える化システムによる算定との突合」を加えた。****第4章 基本目標2に「⑦ 在宅医療・介護連携の推進」を新設し、国の評価指標が求める4つの場面（日常の療養支援・入退院支援・急変時の対応・看取り）ごとの目指すべき姿を掲げた。****基本目標3① の介護給付適正化の記述を、令和8年度交付金の実際の得点に合わせて訂正した**（主要3事業は3つとも実施、医療情報との突合は全国上位1割。0点はケアプラン点検の実施割合だけ）。**項目別の得点そのものは計画本文には置かず、評価から読み取れる中身と協議会への報告手順のみを書いている。**12施策すべてに現状と課題・施策の方向・主な事業・成果指標を記載。**第2版の未確定158箇所のうち61箇所が解消し97箇所となった。**第2章6（被保険者数・認定者数の見込み）を第10期将来推計用推計人口で確定し、第4章③にサービス見込量・給付費・標準給付費・地域支援事業費の事業別内訳・保険料基準額を入れた。**第5版（9月25日）で令和8年度の置き方を自然体推計に改め、保険料基準額は月額6,402円から6,048円（切上げ6,100円）となった。****9月25日の再検証で、延ばし方を見える化システムの仕様にそろえた**（施設は利用者数一定、居住系・在宅は認定者数で延ばす。月額▲13円）。従前の方式による算定は比較のケースとして残している。**第5章2の進行管理に、保険者機能強化推進交付金等の評価結果を点検項目として加えた**（評価結果を外部の議論の場で検証すること自体が評価指標の要件であるため）</t>
         </is>
       </c>
       <c r="O47" s="19" t="inlineStr">
